--- a/Week 6/retail.xlsx
+++ b/Week 6/retail.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\873446\Office 365 Fontys\TW - ds - ds5\Week 4\python voorbeelden\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Data Science 5/ds5_assignment_group14/Week 6/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2A4D16CEFD10D4417AB2E1BFF73124427636BAE6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57A33037-E7B2-4327-A888-7862BB2DE250}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="7884"/>
+    <workbookView xWindow="-216" yWindow="-216" windowWidth="23472" windowHeight="12672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -161,7 +162,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -194,7 +195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -471,9 +472,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C181"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="67" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2482,15 +2486,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004A262539C92C904585DD8DAEB62D4B9C" ma:contentTypeVersion="15" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="41ce988fa6075a7feb2c1193f1cf4be4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f033d15c-9de3-4438-afcc-4066b3eaa3a4" xmlns:ns3="9698003e-3bd0-412e-8c03-32e4ece41802" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e143b889f0d1bdeebc107067648d52ec" ns2:_="" ns3:_="">
     <xsd:import namespace="f033d15c-9de3-4438-afcc-4066b3eaa3a4"/>
@@ -2713,6 +2708,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C324E9F8-E6A9-48E7-8006-BD0484ADC6CC}">
   <ds:schemaRefs>
@@ -2731,13 +2735,28 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8D98B6D-E06D-49FD-A1A5-F4352881B8AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f033d15c-9de3-4438-afcc-4066b3eaa3a4"/>
+    <ds:schemaRef ds:uri="9698003e-3bd0-412e-8c03-32e4ece41802"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD83FB53-9E8C-4CCD-9AD9-795BC9AB81B7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8D98B6D-E06D-49FD-A1A5-F4352881B8AE}"/>
 </file>